--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1117,1394 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121589787</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>649754</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7170132</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121589781</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>649653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7170246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121589778</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>649707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7170108</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121589789</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>649849</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7170087</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121589782</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>649633</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7170230</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121589786</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>649766</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7170201</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121589788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>649927</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7170078</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121589779</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>649708</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7170285</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121589785</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>649729</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7170230</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121589790</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>649837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7170108</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121589784</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>649702</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7170233</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121589780</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>649660</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7170277</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121589783</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>649652</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7170226</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589787</v>
+        <v>121589788</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649754</v>
+        <v>649927</v>
       </c>
       <c r="R6" t="n">
-        <v>7170132</v>
+        <v>7170078</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589781</v>
+        <v>121589780</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649653</v>
+        <v>649660</v>
       </c>
       <c r="R7" t="n">
-        <v>7170246</v>
+        <v>7170277</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589778</v>
+        <v>121589779</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649707</v>
+        <v>649708</v>
       </c>
       <c r="R8" t="n">
-        <v>7170108</v>
+        <v>7170285</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589782</v>
+        <v>121589786</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1565,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649633</v>
+        <v>649766</v>
       </c>
       <c r="R10" t="n">
-        <v>7170230</v>
+        <v>7170201</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589786</v>
+        <v>121589787</v>
       </c>
       <c r="B11" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1671,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1698,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649766</v>
+        <v>649754</v>
       </c>
       <c r="R11" t="n">
-        <v>7170201</v>
+        <v>7170132</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589788</v>
+        <v>121589778</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1804,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649927</v>
+        <v>649707</v>
       </c>
       <c r="R12" t="n">
-        <v>7170078</v>
+        <v>7170108</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589779</v>
+        <v>121589782</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1910,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649708</v>
+        <v>649633</v>
       </c>
       <c r="R13" t="n">
-        <v>7170285</v>
+        <v>7170230</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,11 +1951,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589785</v>
+        <v>121589781</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,25 +1989,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649729</v>
+        <v>649653</v>
       </c>
       <c r="R14" t="n">
-        <v>7170230</v>
+        <v>7170246</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589780</v>
+        <v>121589785</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,25 +2307,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649660</v>
+        <v>649729</v>
       </c>
       <c r="R17" t="n">
-        <v>7170277</v>
+        <v>7170230</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589788</v>
+        <v>121589784</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649927</v>
+        <v>649702</v>
       </c>
       <c r="R6" t="n">
-        <v>7170078</v>
+        <v>7170233</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589780</v>
+        <v>121589782</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649660</v>
+        <v>649633</v>
       </c>
       <c r="R7" t="n">
-        <v>7170277</v>
+        <v>7170230</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589779</v>
+        <v>121589781</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649708</v>
+        <v>649653</v>
       </c>
       <c r="R8" t="n">
-        <v>7170285</v>
+        <v>7170246</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,11 +1411,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589789</v>
+        <v>121589778</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649849</v>
+        <v>649707</v>
       </c>
       <c r="R9" t="n">
-        <v>7170087</v>
+        <v>7170108</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,11 +1517,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589786</v>
+        <v>121589780</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1597,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649766</v>
+        <v>649660</v>
       </c>
       <c r="R10" t="n">
-        <v>7170201</v>
+        <v>7170277</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589787</v>
+        <v>121589788</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1703,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649754</v>
+        <v>649927</v>
       </c>
       <c r="R11" t="n">
-        <v>7170132</v>
+        <v>7170078</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589778</v>
+        <v>121589785</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1809,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649707</v>
+        <v>649729</v>
       </c>
       <c r="R12" t="n">
-        <v>7170108</v>
+        <v>7170230</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589782</v>
+        <v>121589786</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1915,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649633</v>
+        <v>649766</v>
       </c>
       <c r="R13" t="n">
-        <v>7170230</v>
+        <v>7170201</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589781</v>
+        <v>121589789</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649653</v>
+        <v>649849</v>
       </c>
       <c r="R14" t="n">
-        <v>7170246</v>
+        <v>7170087</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,6 +2047,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589790</v>
+        <v>121589787</v>
       </c>
       <c r="B15" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,25 +2090,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649837</v>
+        <v>649754</v>
       </c>
       <c r="R15" t="n">
-        <v>7170108</v>
+        <v>7170132</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2189,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589784</v>
+        <v>121589790</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,25 +2196,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2233,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649702</v>
+        <v>649837</v>
       </c>
       <c r="R16" t="n">
-        <v>7170233</v>
+        <v>7170108</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2295,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589785</v>
+        <v>121589779</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,25 +2302,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2339,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649729</v>
+        <v>649708</v>
       </c>
       <c r="R17" t="n">
-        <v>7170230</v>
+        <v>7170285</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,6 +2370,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589784</v>
+        <v>121589780</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649702</v>
+        <v>649660</v>
       </c>
       <c r="R6" t="n">
-        <v>7170233</v>
+        <v>7170277</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589782</v>
+        <v>121589779</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649633</v>
+        <v>649708</v>
       </c>
       <c r="R7" t="n">
-        <v>7170230</v>
+        <v>7170285</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,6 +1305,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589781</v>
+        <v>121589778</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649653</v>
+        <v>649707</v>
       </c>
       <c r="R8" t="n">
-        <v>7170246</v>
+        <v>7170108</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589778</v>
+        <v>121589782</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649707</v>
+        <v>649633</v>
       </c>
       <c r="R9" t="n">
-        <v>7170108</v>
+        <v>7170230</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589780</v>
+        <v>121589787</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649660</v>
+        <v>649754</v>
       </c>
       <c r="R10" t="n">
-        <v>7170277</v>
+        <v>7170132</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589788</v>
+        <v>121589789</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649927</v>
+        <v>649849</v>
       </c>
       <c r="R11" t="n">
-        <v>7170078</v>
+        <v>7170087</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1729,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589785</v>
+        <v>121589788</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649729</v>
+        <v>649927</v>
       </c>
       <c r="R12" t="n">
-        <v>7170230</v>
+        <v>7170078</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589786</v>
+        <v>121589784</v>
       </c>
       <c r="B13" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1883,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649766</v>
+        <v>649702</v>
       </c>
       <c r="R13" t="n">
-        <v>7170201</v>
+        <v>7170233</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589789</v>
+        <v>121589785</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1989,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649849</v>
+        <v>649729</v>
       </c>
       <c r="R14" t="n">
-        <v>7170087</v>
+        <v>7170230</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2047,11 +2057,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589787</v>
+        <v>121589790</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2095,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2122,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649754</v>
+        <v>649837</v>
       </c>
       <c r="R15" t="n">
-        <v>7170132</v>
+        <v>7170108</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589790</v>
+        <v>121589786</v>
       </c>
       <c r="B16" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649837</v>
+        <v>649766</v>
       </c>
       <c r="R16" t="n">
-        <v>7170108</v>
+        <v>7170201</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589779</v>
+        <v>121589781</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2334,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649708</v>
+        <v>649653</v>
       </c>
       <c r="R17" t="n">
-        <v>7170285</v>
+        <v>7170246</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2370,11 +2375,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,7 +2404,7 @@
         <v>121589783</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589786</v>
+        <v>121589789</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649766</v>
+        <v>649849</v>
       </c>
       <c r="R6" t="n">
-        <v>7170201</v>
+        <v>7170087</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,6 +1199,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589789</v>
+        <v>121589790</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649849</v>
+        <v>649837</v>
       </c>
       <c r="R7" t="n">
-        <v>7170087</v>
+        <v>7170108</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,11 +1310,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589778</v>
+        <v>121589780</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649707</v>
+        <v>649660</v>
       </c>
       <c r="R8" t="n">
-        <v>7170108</v>
+        <v>7170277</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589779</v>
+        <v>121589788</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649708</v>
+        <v>649927</v>
       </c>
       <c r="R9" t="n">
-        <v>7170285</v>
+        <v>7170078</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,11 +1522,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589783</v>
+        <v>121589786</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649652</v>
+        <v>649766</v>
       </c>
       <c r="R10" t="n">
-        <v>7170226</v>
+        <v>7170201</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1659,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589780</v>
+        <v>121589778</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1703,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649660</v>
+        <v>649707</v>
       </c>
       <c r="R11" t="n">
-        <v>7170277</v>
+        <v>7170108</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589788</v>
+        <v>121589782</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1809,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649927</v>
+        <v>649633</v>
       </c>
       <c r="R12" t="n">
-        <v>7170078</v>
+        <v>7170230</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589785</v>
+        <v>121589787</v>
       </c>
       <c r="B13" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1878,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649729</v>
+        <v>649754</v>
       </c>
       <c r="R13" t="n">
-        <v>7170230</v>
+        <v>7170132</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589784</v>
+        <v>121589785</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649702</v>
+        <v>649729</v>
       </c>
       <c r="R14" t="n">
-        <v>7170233</v>
+        <v>7170230</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2083,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589787</v>
+        <v>121589779</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,21 +2094,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649754</v>
+        <v>649708</v>
       </c>
       <c r="R15" t="n">
-        <v>7170132</v>
+        <v>7170285</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,6 +2158,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589782</v>
+        <v>121589781</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649633</v>
+        <v>649653</v>
       </c>
       <c r="R16" t="n">
-        <v>7170230</v>
+        <v>7170246</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589781</v>
+        <v>121589783</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649653</v>
+        <v>649652</v>
       </c>
       <c r="R17" t="n">
-        <v>7170246</v>
+        <v>7170226</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589790</v>
+        <v>121589784</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2413,25 +2413,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649837</v>
+        <v>649702</v>
       </c>
       <c r="R18" t="n">
-        <v>7170108</v>
+        <v>7170233</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 55329-2019 artfynd.xlsx
+++ b/artfynd/A 55329-2019 artfynd.xlsx
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589789</v>
+        <v>121589782</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649849</v>
+        <v>649633</v>
       </c>
       <c r="R6" t="n">
-        <v>7170087</v>
+        <v>7170230</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,11 +1199,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589790</v>
+        <v>121589780</v>
       </c>
       <c r="B7" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649837</v>
+        <v>649660</v>
       </c>
       <c r="R7" t="n">
-        <v>7170108</v>
+        <v>7170277</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589780</v>
+        <v>121589781</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1380,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649660</v>
+        <v>649653</v>
       </c>
       <c r="R8" t="n">
-        <v>7170277</v>
+        <v>7170246</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589788</v>
+        <v>121589786</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649927</v>
+        <v>649766</v>
       </c>
       <c r="R9" t="n">
-        <v>7170078</v>
+        <v>7170201</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1548,7 +1543,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589786</v>
+        <v>121589790</v>
       </c>
       <c r="B10" t="n">
         <v>97067</v>
@@ -1592,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649766</v>
+        <v>649837</v>
       </c>
       <c r="R10" t="n">
-        <v>7170201</v>
+        <v>7170108</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589778</v>
+        <v>121589785</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1661,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1698,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649707</v>
+        <v>649729</v>
       </c>
       <c r="R11" t="n">
-        <v>7170108</v>
+        <v>7170230</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589782</v>
+        <v>121589788</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1804,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>649633</v>
+        <v>649927</v>
       </c>
       <c r="R12" t="n">
-        <v>7170230</v>
+        <v>7170078</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589787</v>
+        <v>121589783</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>649754</v>
+        <v>649652</v>
       </c>
       <c r="R13" t="n">
-        <v>7170132</v>
+        <v>7170226</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589785</v>
+        <v>121589789</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2016,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649729</v>
+        <v>649849</v>
       </c>
       <c r="R14" t="n">
-        <v>7170230</v>
+        <v>7170087</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2052,6 +2047,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589781</v>
+        <v>121589784</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649653</v>
+        <v>649702</v>
       </c>
       <c r="R16" t="n">
-        <v>7170246</v>
+        <v>7170233</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589783</v>
+        <v>121589787</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649652</v>
+        <v>649754</v>
       </c>
       <c r="R17" t="n">
-        <v>7170226</v>
+        <v>7170132</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589784</v>
+        <v>121589778</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649702</v>
+        <v>649707</v>
       </c>
       <c r="R18" t="n">
-        <v>7170233</v>
+        <v>7170108</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
